--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104732080</v>
+        <v>104730188</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609703.1254453886</v>
+        <v>609902</v>
       </c>
       <c r="R2" t="n">
-        <v>7011999.583781821</v>
+        <v>7012023</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -788,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104734974</v>
+        <v>104730287</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,37 +794,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N om Österåsens hälsohem, Österås, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609797.9241411095</v>
+        <v>609852</v>
       </c>
       <c r="R3" t="n">
-        <v>7012015.89822578</v>
+        <v>7012050</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +873,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104730483</v>
+        <v>104731954</v>
       </c>
       <c r="B4" t="n">
-        <v>77507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +902,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230405</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609999.0367894287</v>
+        <v>609761</v>
       </c>
       <c r="R4" t="n">
-        <v>7012161.298588103</v>
+        <v>7011978</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1017,15 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104730188</v>
+        <v>104731982</v>
       </c>
       <c r="B5" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,12 +1019,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609901.6210389532</v>
+        <v>609742</v>
       </c>
       <c r="R5" t="n">
-        <v>7012023.041511572</v>
+        <v>7011977</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1130,15 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104730004</v>
+        <v>104732087</v>
       </c>
       <c r="B6" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,21 +1118,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609919.3520714133</v>
+        <v>609704</v>
       </c>
       <c r="R6" t="n">
-        <v>7011993.408900177</v>
+        <v>7011998</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1243,15 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104730461</v>
+        <v>104732381</v>
       </c>
       <c r="B7" t="n">
-        <v>77507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230405</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609975.135005486</v>
+        <v>609751</v>
       </c>
       <c r="R7" t="n">
-        <v>7012173.118974193</v>
+        <v>7011984</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1356,15 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104730320</v>
+        <v>104734991</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,35 +1334,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>N om Österåsens hälsohem, Österås, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609892.082559926</v>
+        <v>609798</v>
       </c>
       <c r="R8" t="n">
-        <v>7012064.235436399</v>
+        <v>7012016</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1430,27 +1394,18 @@
           <t>2022-11-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-18</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1469,15 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104730336</v>
+        <v>104735022</v>
       </c>
       <c r="B9" t="n">
-        <v>77507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,35 +1435,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230405</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>N om Österåsens hälsohem, Österås, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609883.7448123274</v>
+        <v>609925</v>
       </c>
       <c r="R9" t="n">
-        <v>7012109.982617969</v>
+        <v>7011998</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1543,27 +1495,18 @@
           <t>2022-11-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-18</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1582,15 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104730114</v>
+        <v>111957798</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,38 +1536,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Österåsen, Österås, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609923.4088923346</v>
+        <v>609747</v>
       </c>
       <c r="R10" t="n">
-        <v>7011980.459442987</v>
+        <v>7011953</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,22 +1601,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,33 +1615,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Lennart Vessberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Lennart Vessberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104731941</v>
+        <v>111957843</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1711,38 +1645,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Österås, Österås, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609750.6558443242</v>
+        <v>609773</v>
       </c>
       <c r="R11" t="n">
-        <v>7011957.425075077</v>
+        <v>7011992</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1766,22 +1710,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,33 +1724,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Lennart Vessberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Lennart Vessberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104734991</v>
+        <v>111957952</v>
       </c>
       <c r="B12" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1833,31 +1763,39 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N om Österåsens hälsohem, Österås, Ång</t>
+          <t>Österåsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609797.9241411095</v>
+        <v>609820</v>
       </c>
       <c r="R12" t="n">
-        <v>7012015.89822578</v>
+        <v>7011919</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1881,22 +1819,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,27 +1840,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Lennart Vessberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Lennart Vessberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104730081</v>
+        <v>132690131</v>
       </c>
       <c r="B13" t="n">
-        <v>77507</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,38 +1863,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230405</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609902.0205275981</v>
+        <v>609785</v>
       </c>
       <c r="R13" t="n">
-        <v>7012011.321389751</v>
+        <v>7011912</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,22 +1917,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,15 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104731982</v>
+        <v>104730114</v>
       </c>
       <c r="B14" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2078,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609742.2916457441</v>
+        <v>609923</v>
       </c>
       <c r="R14" t="n">
-        <v>7011977.449014347</v>
+        <v>7011981</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2150,15 +2057,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104735022</v>
+        <v>104730320</v>
       </c>
       <c r="B15" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,37 +2068,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>N om Österåsens hälsohem, Österås, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609925.0511431585</v>
+        <v>609893</v>
       </c>
       <c r="R15" t="n">
-        <v>7011998.567500393</v>
+        <v>7012064</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2228,7 +2128,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,7 +2138,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,7 +2147,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2266,15 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104730419</v>
+        <v>104731941</v>
       </c>
       <c r="B16" t="n">
-        <v>77507</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2282,21 +2176,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>230405</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2307,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609955.1769725434</v>
+        <v>609750</v>
       </c>
       <c r="R16" t="n">
-        <v>7012162.058878846</v>
+        <v>7011957</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2379,15 +2273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104731954</v>
+        <v>104732080</v>
       </c>
       <c r="B17" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,21 +2284,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2420,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609760.332139757</v>
+        <v>609704</v>
       </c>
       <c r="R17" t="n">
-        <v>7011978.514387502</v>
+        <v>7012000</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2492,15 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104730107</v>
+        <v>104732149</v>
       </c>
       <c r="B18" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2508,21 +2392,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2533,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609923.4088923346</v>
+        <v>609697</v>
       </c>
       <c r="R18" t="n">
-        <v>7011980.459442987</v>
+        <v>7012035</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2605,15 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104730200</v>
+        <v>104734974</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,35 +2500,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>N om Österåsens hälsohem, Österås, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609910.9004636746</v>
+        <v>609798</v>
       </c>
       <c r="R19" t="n">
-        <v>7012029.224674962</v>
+        <v>7012016</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,27 +2560,18 @@
           <t>2022-11-18</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-11-18</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2718,37 +2590,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104732087</v>
+        <v>104730004</v>
       </c>
       <c r="B20" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2759,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609703.1561196814</v>
+        <v>609919</v>
       </c>
       <c r="R20" t="n">
-        <v>7011998.68222943</v>
+        <v>7011993</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2831,37 +2698,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104732149</v>
+        <v>104730107</v>
       </c>
       <c r="B21" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2872,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609697.8666614152</v>
+        <v>609923</v>
       </c>
       <c r="R21" t="n">
-        <v>7012034.605909345</v>
+        <v>7011981</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2944,15 +2806,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104732381</v>
+        <v>111958248</v>
       </c>
       <c r="B22" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,38 +2817,48 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>4412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Österåsen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609750.1866178951</v>
+        <v>609824</v>
       </c>
       <c r="R22" t="n">
-        <v>7011984.487250591</v>
+        <v>7011907</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3015,22 +2882,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3039,55 +2896,51 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Lennart Vessberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Lennart Vessberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104730287</v>
+        <v>104730200</v>
       </c>
       <c r="B23" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3098,10 +2951,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609851.4519852737</v>
+        <v>609910</v>
       </c>
       <c r="R23" t="n">
-        <v>7012049.763410183</v>
+        <v>7012030</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3170,50 +3023,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111957798</v>
+        <v>111958182</v>
       </c>
       <c r="B24" t="n">
-        <v>89834</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3259,13 +3108,17 @@
           <t>2023-09-04</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3284,61 +3137,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111957843</v>
+        <v>111958205</v>
       </c>
       <c r="B25" t="n">
-        <v>89834</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Österås, Österås, Ång</t>
+          <t>Österåsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609773</v>
+        <v>609803</v>
       </c>
       <c r="R25" t="n">
-        <v>7011992</v>
+        <v>7011969</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3371,6 +3220,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>½ m2</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3398,65 +3252,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111958182</v>
+        <v>104730081</v>
       </c>
       <c r="B26" t="n">
-        <v>55643</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>230405</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Österåsen, Österås, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609747</v>
+        <v>609902</v>
       </c>
       <c r="R26" t="n">
-        <v>7011953</v>
+        <v>7012011</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3480,17 +3318,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1K</t>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3505,27 +3348,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lennart Vessberg</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lennart Vessberg</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111958205</v>
+        <v>104730336</v>
       </c>
       <c r="B27" t="n">
-        <v>96735</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3533,49 +3371,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>230405</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Österåsen, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609803</v>
+        <v>609883</v>
       </c>
       <c r="R27" t="n">
-        <v>7011969</v>
+        <v>7012110</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3599,17 +3426,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>½ m2</t>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3618,22 +3450,453 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lennart Vessberg</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lennart Vessberg</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>104730419</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>609955</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7012162</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>104730461</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>609975</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7012174</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>104730483</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>609999</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7012162</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>104730501</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>610046</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7012129</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730188</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730287</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104731954</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104731982</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104732087</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104732381</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104734991</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104735022</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,6 +1676,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111957798</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1740,6 +1790,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111957843</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111957952</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132690131</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2054,6 +2119,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730114</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2162,6 +2232,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730320</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2270,6 +2345,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104731941</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2378,6 +2458,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104732080</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2486,6 +2571,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104732149</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2587,6 +2677,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104734974</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2695,6 +2790,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730004</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2803,6 +2903,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730107</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2912,6 +3017,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111958248</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3020,6 +3130,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730200</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3134,6 +3249,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111958182</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3249,6 +3369,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111958205</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3357,6 +3482,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730081</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3465,6 +3595,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730336</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3573,6 +3708,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730419</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3681,6 +3821,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730461</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3789,6 +3934,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730483</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3897,8 +4047,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730501</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>